--- a/inasistencias-5a-InstrumentalYsistElect/alumnos-5a-InstrumentalYsistElect.xlsx
+++ b/inasistencias-5a-InstrumentalYsistElect/alumnos-5a-InstrumentalYsistElect.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2854" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2863" uniqueCount="683">
   <si>
     <t xml:space="preserve">total </t>
   </si>
@@ -464,6 +464,9 @@
     <t xml:space="preserve">recupear con</t>
   </si>
   <si>
+    <t xml:space="preserve">Casas</t>
+  </si>
+  <si>
     <t xml:space="preserve">15-Diag en blo-Radar primario</t>
   </si>
   <si>
@@ -485,6 +488,9 @@
     <t xml:space="preserve">Casas y Chaya</t>
   </si>
   <si>
+    <t xml:space="preserve">ausente</t>
+  </si>
+  <si>
     <t xml:space="preserve">tiene dimensiones viva</t>
   </si>
   <si>
@@ -494,10 +500,19 @@
     <t xml:space="preserve">no demostro conocimiento</t>
   </si>
   <si>
+    <t xml:space="preserve">Ausente</t>
+  </si>
+  <si>
     <t xml:space="preserve">no puedo acceder</t>
   </si>
   <si>
     <t xml:space="preserve">Rivero  Montesino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aprobador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reprobado</t>
   </si>
   <si>
     <t xml:space="preserve">---</t>
@@ -2088,13 +2103,12 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2116,31 +2130,32 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF127622"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3465A4"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF355269"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2162,18 +2177,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9800"/>
-        <bgColor rgb="FFFFC107"/>
+        <bgColor rgb="FFE8A202"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
+        <bgColor rgb="FFE8A202"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4000"/>
+        <bgColor rgb="FFF10D0C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8A202"/>
         <bgColor rgb="FFFF9800"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF4000"/>
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF10D0C"/>
         <bgColor rgb="FFCC0000"/>
       </patternFill>
     </fill>
@@ -2219,7 +2252,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2316,7 +2349,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2329,11 +2390,10 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -2347,7 +2407,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FFCC0000"/>
         <sz val="12"/>
@@ -2361,7 +2420,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -2376,7 +2434,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -2391,7 +2448,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -2406,7 +2462,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -2420,7 +2475,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FFCC0000"/>
         <sz val="12"/>
@@ -2434,7 +2488,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -2449,7 +2502,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -2463,7 +2515,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FF006600"/>
         <sz val="12"/>
@@ -2477,7 +2528,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <color rgb="FFCC0000"/>
         <sz val="12"/>
@@ -2491,7 +2541,6 @@
     <dxf>
       <font>
         <name val="Calibri"/>
-        <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
         <color rgb="FFFFFFFF"/>
@@ -2503,18 +2552,44 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FFF10D0C"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF127622"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -2527,7 +2602,7 @@
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFE8A202"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
@@ -2548,7 +2623,7 @@
       <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFC107"/>
       <rgbColor rgb="FFFF9800"/>
       <rgbColor rgb="FFFF4000"/>
@@ -6573,19 +6648,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>138</v>
@@ -6596,10 +6671,10 @@
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>6</v>
@@ -6621,10 +6696,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>6</v>
@@ -6635,10 +6710,10 @@
         <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>5</v>
@@ -6649,10 +6724,10 @@
         <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>4</v>
@@ -6663,10 +6738,10 @@
         <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8</v>
@@ -6688,10 +6763,10 @@
         <v>97</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>5</v>
@@ -6702,10 +6777,10 @@
         <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
@@ -6716,10 +6791,10 @@
         <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>4</v>
@@ -6730,10 +6805,10 @@
         <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>3</v>
@@ -6744,10 +6819,10 @@
         <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>3</v>
@@ -6758,10 +6833,10 @@
         <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>2</v>
@@ -6772,10 +6847,10 @@
         <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>2</v>
@@ -6786,10 +6861,10 @@
         <v>108</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>7</v>
@@ -6811,10 +6886,10 @@
         <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>6</v>
@@ -6825,10 +6900,10 @@
         <v>108</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>5</v>
@@ -6839,10 +6914,10 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>5</v>
@@ -6853,10 +6928,10 @@
         <v>108</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>5</v>
@@ -6867,10 +6942,10 @@
         <v>108</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>3</v>
@@ -6905,13 +6980,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6936,10 +7011,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -6950,7 +7025,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -6986,19 +7061,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -7015,10 +7090,10 @@
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9.5</v>
@@ -7038,10 +7113,10 @@
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8.33</v>
@@ -7061,10 +7136,10 @@
         <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -7084,10 +7159,10 @@
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9.5</v>
@@ -7107,10 +7182,10 @@
         <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -7130,10 +7205,10 @@
         <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -7153,10 +7228,10 @@
         <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -7176,10 +7251,10 @@
         <v>59</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -7199,10 +7274,10 @@
         <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9.5</v>
@@ -7236,10 +7311,10 @@
         <v>71</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -7259,10 +7334,10 @@
         <v>74</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -7282,10 +7357,10 @@
         <v>77</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9.33</v>
@@ -7305,10 +7380,10 @@
         <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9.33</v>
@@ -7328,10 +7403,10 @@
         <v>83</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9.33</v>
@@ -7351,10 +7426,10 @@
         <v>86</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -7374,10 +7449,10 @@
         <v>89</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9.42</v>
@@ -7397,10 +7472,10 @@
         <v>94</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9.33</v>
@@ -7422,10 +7497,10 @@
         <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.33</v>
@@ -7436,10 +7511,10 @@
         <v>94</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>3</v>
@@ -7456,10 +7531,10 @@
         <v>97</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9.42</v>
@@ -7479,10 +7554,10 @@
         <v>102</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -7502,10 +7577,10 @@
         <v>105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -7525,10 +7600,10 @@
         <v>108</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -7542,7 +7617,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7588,13 +7663,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7619,10 +7694,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -7633,7 +7708,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -7669,19 +7744,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -7712,10 +7787,10 @@
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -7735,10 +7810,10 @@
         <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -7758,10 +7833,10 @@
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -7783,10 +7858,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -7803,10 +7878,10 @@
         <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -7826,10 +7901,10 @@
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -7851,10 +7926,10 @@
         <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -7865,10 +7940,10 @@
         <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
@@ -7879,10 +7954,10 @@
         <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>6</v>
@@ -7893,10 +7968,10 @@
         <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -7907,10 +7982,10 @@
         <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>5</v>
@@ -7927,10 +8002,10 @@
         <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -7950,10 +8025,10 @@
         <v>59</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -7975,10 +8050,10 @@
         <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -7989,10 +8064,10 @@
         <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -8003,10 +8078,10 @@
         <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8017,10 +8092,10 @@
         <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -8031,10 +8106,10 @@
         <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -8045,10 +8120,10 @@
         <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>4</v>
@@ -8065,10 +8140,10 @@
         <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -8088,10 +8163,10 @@
         <v>67</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>3</v>
@@ -8125,10 +8200,10 @@
         <v>74</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -8162,10 +8237,10 @@
         <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>5</v>
@@ -8185,10 +8260,10 @@
         <v>83</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -8236,10 +8311,10 @@
         <v>94</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -8287,10 +8362,10 @@
         <v>105</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>8</v>
@@ -8310,10 +8385,10 @@
         <v>108</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>8</v>
@@ -8327,7 +8402,7 @@
         <v>25</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8376,13 +8451,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8407,10 +8482,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -8421,7 +8496,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -8456,13 +8531,13 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8470,10 +8545,10 @@
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -8487,10 +8562,10 @@
         <v>67</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>5</v>
@@ -8512,10 +8587,10 @@
         <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>3</v>
@@ -8526,10 +8601,10 @@
         <v>71</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>7</v>
@@ -8540,10 +8615,10 @@
         <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8</v>
@@ -8565,10 +8640,10 @@
         <v>89</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>7</v>
@@ -8579,10 +8654,10 @@
         <v>89</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>6</v>
@@ -8593,10 +8668,10 @@
         <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>5</v>
@@ -8607,10 +8682,10 @@
         <v>89</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
@@ -8621,10 +8696,10 @@
         <v>89</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
@@ -8635,10 +8710,10 @@
         <v>89</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>4</v>
@@ -8649,10 +8724,10 @@
         <v>89</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>3</v>
@@ -8663,10 +8738,10 @@
         <v>89</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>3</v>
@@ -8677,10 +8752,10 @@
         <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>7</v>
@@ -8702,10 +8777,10 @@
         <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>2</v>
@@ -8716,10 +8791,10 @@
         <v>97</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -8730,10 +8805,10 @@
         <v>102</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>7</v>
@@ -8755,10 +8830,10 @@
         <v>102</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>6</v>
@@ -8769,10 +8844,10 @@
         <v>102</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>5</v>
@@ -8783,10 +8858,10 @@
         <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>5</v>
@@ -8797,10 +8872,10 @@
         <v>102</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>5</v>
@@ -8811,10 +8886,10 @@
         <v>102</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>2</v>
@@ -8850,13 +8925,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8881,10 +8956,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -8895,7 +8970,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -8937,19 +9012,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -8966,10 +9041,10 @@
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -8989,10 +9064,10 @@
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -9012,10 +9087,10 @@
         <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -9035,10 +9110,10 @@
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -9060,10 +9135,10 @@
         <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>9</v>
@@ -9074,10 +9149,10 @@
         <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -9088,10 +9163,10 @@
         <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -9102,10 +9177,10 @@
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -9125,10 +9200,10 @@
         <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -9150,10 +9225,10 @@
         <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -9164,10 +9239,10 @@
         <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -9178,10 +9253,10 @@
         <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>6</v>
@@ -9192,10 +9267,10 @@
         <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
@@ -9206,10 +9281,10 @@
         <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>5</v>
@@ -9220,10 +9295,10 @@
         <v>45</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>5</v>
@@ -9254,10 +9329,10 @@
         <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -9279,10 +9354,10 @@
         <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>5</v>
@@ -9299,10 +9374,10 @@
         <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -9322,10 +9397,10 @@
         <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -9347,10 +9422,10 @@
         <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -9361,10 +9436,10 @@
         <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -9375,10 +9450,10 @@
         <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>6</v>
@@ -9409,10 +9484,10 @@
         <v>71</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -9432,10 +9507,10 @@
         <v>74</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -9455,10 +9530,10 @@
         <v>77</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>7</v>
@@ -9480,10 +9555,10 @@
         <v>77</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>5</v>
@@ -9494,10 +9569,10 @@
         <v>77</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>4</v>
@@ -9514,10 +9589,10 @@
         <v>80</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>9</v>
@@ -9539,10 +9614,10 @@
         <v>80</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
@@ -9553,10 +9628,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>6</v>
@@ -9567,10 +9642,10 @@
         <v>80</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>5</v>
@@ -9587,10 +9662,10 @@
         <v>83</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -9638,10 +9713,10 @@
         <v>94</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -9661,10 +9736,10 @@
         <v>97</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>8</v>
@@ -9686,10 +9761,10 @@
         <v>97</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>7</v>
@@ -9706,10 +9781,10 @@
         <v>102</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>10</v>
@@ -9729,10 +9804,10 @@
         <v>105</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -9754,10 +9829,10 @@
         <v>105</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>8</v>
@@ -9768,10 +9843,10 @@
         <v>105</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>7</v>
@@ -9782,10 +9857,10 @@
         <v>105</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>5</v>
@@ -9810,16 +9885,16 @@
         <v>25</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>10</v>
@@ -9873,16 +9948,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>138</v>
@@ -9899,7 +9974,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>9</v>
@@ -9919,7 +9994,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>9</v>
@@ -9939,7 +10014,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>9</v>
@@ -9959,7 +10034,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>9</v>
@@ -9993,7 +10068,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>10</v>
@@ -10015,7 +10090,7 @@
         <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>6</v>
@@ -10046,7 +10121,7 @@
         <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>7</v>
@@ -10080,7 +10155,7 @@
         <v>59</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>10</v>
@@ -10102,7 +10177,7 @@
         <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>10</v>
@@ -10113,7 +10188,7 @@
         <v>59</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>9</v>
@@ -10124,7 +10199,7 @@
         <v>59</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>9</v>
@@ -10135,7 +10210,7 @@
         <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>9</v>
@@ -10146,7 +10221,7 @@
         <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>8</v>
@@ -10163,7 +10238,7 @@
         <v>63</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>1</v>
@@ -10197,7 +10272,7 @@
         <v>71</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>7</v>
@@ -10217,7 +10292,7 @@
         <v>74</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>10</v>
@@ -10237,7 +10312,7 @@
         <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>8</v>
@@ -10257,7 +10332,7 @@
         <v>80</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>8</v>
@@ -10279,7 +10354,7 @@
         <v>80</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>7</v>
@@ -10296,7 +10371,7 @@
         <v>83</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>10</v>
@@ -10316,7 +10391,7 @@
         <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>9</v>
@@ -10338,7 +10413,7 @@
         <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>8</v>
@@ -10349,7 +10424,7 @@
         <v>86</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>2</v>
@@ -10366,7 +10441,7 @@
         <v>89</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>8</v>
@@ -10380,7 +10455,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>1</v>
@@ -10400,7 +10475,7 @@
         <v>94</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>3</v>
@@ -10420,7 +10495,7 @@
         <v>97</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>8</v>
@@ -10442,7 +10517,7 @@
         <v>97</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>6</v>
@@ -10459,7 +10534,7 @@
         <v>102</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>9</v>
@@ -10479,7 +10554,7 @@
         <v>105</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>9</v>
@@ -10501,7 +10576,7 @@
         <v>105</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>8</v>
@@ -10512,7 +10587,7 @@
         <v>105</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>5</v>
@@ -10526,7 +10601,7 @@
         <v>108</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>9</v>
@@ -10562,24 +10637,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BA28"/>
+  <dimension ref="A1:BE29"/>
   <sheetFormatPr defaultColWidth="9.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.2"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="3" style="1" width="9.39"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="16" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="17" style="1" width="11.19"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="1" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="8.57"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="22" min="22" style="1" width="8.57"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="23" style="1" width="9.93"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="25" min="24" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="8.57"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="35" min="27" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="3" style="1" width="9.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="11.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="9.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="8.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="27" style="1" width="9.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="13.66"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="12.47"/>
@@ -10587,10 +10661,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="15.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="46" min="42" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="12.41"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="9.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="49" style="1" width="11.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="25.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="20"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="52" min="48" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="53" style="1" width="11.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="25.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10617,6 +10691,9 @@
       <c r="AU1" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="AV1" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -10749,22 +10826,31 @@
         <v>140</v>
       </c>
       <c r="AW2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AX2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AY2" s="3" t="s">
+      <c r="BB2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AZ2" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BA2" s="3" t="s">
+      <c r="BD2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE2" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -10889,22 +10975,22 @@
         <v>8</v>
       </c>
       <c r="AT3" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AV3" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AY3" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BC3" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
@@ -11026,22 +11112,33 @@
         <v>12</v>
       </c>
       <c r="AV4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX4" s="1" t="n">
+        <f aca="false">ROUND(AQ4*6/10,0)</f>
+        <v>4</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX4" s="6" t="n">
+        <f aca="false">MIN(AW4,AV4)</f>
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AY4" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AZ4" s="1" t="n">
+      <c r="BC4" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="BA4" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BE4" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -11161,16 +11258,20 @@
         <v>8</v>
       </c>
       <c r="AV5" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" s="6"/>
+      <c r="AZ5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AY5" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BC5" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -11288,16 +11389,20 @@
         <v>8</v>
       </c>
       <c r="AV6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX6" s="6"/>
+      <c r="AZ6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AY6" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BC6" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>25</v>
       </c>
@@ -11423,13 +11528,24 @@
         <v>5</v>
       </c>
       <c r="AU7" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV7" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <f aca="false">ROUND(AQ7*6/10,0)</f>
+        <v>4</v>
+      </c>
+      <c r="AW7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX7" s="6" t="n">
+        <f aca="false">MIN(AW7,AV7)</f>
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
@@ -11546,13 +11662,17 @@
         <v>8</v>
       </c>
       <c r="AV8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX8" s="1" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+      <c r="AX8" s="6"/>
+      <c r="AZ8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB8" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -11682,13 +11802,17 @@
         <v>9</v>
       </c>
       <c r="AV9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX9" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+      <c r="AX9" s="6"/>
+      <c r="AZ9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB9" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -11808,22 +11932,26 @@
         <v>8</v>
       </c>
       <c r="AV10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX10" s="6"/>
+      <c r="AZ10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AY10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AZ10" s="1" t="n">
+      <c r="BC10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BD10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="BA10" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BE10" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>26</v>
       </c>
@@ -11930,16 +12058,29 @@
         <v>2</v>
       </c>
       <c r="AU11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV11" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="AV11" s="1" t="n">
+        <f aca="false">ROUND(AQ11*6/10,0)</f>
         <v>1</v>
       </c>
-      <c r="AX11" s="2" t="n">
+      <c r="AW11" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AZ11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
@@ -12059,14 +12200,18 @@
       <c r="AV12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AX12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY12" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX12" s="6"/>
+      <c r="AZ12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC12" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
@@ -12186,13 +12331,17 @@
         <v>8</v>
       </c>
       <c r="AV13" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX13" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+      <c r="AX13" s="6"/>
+      <c r="AZ13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB13" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>11</v>
       </c>
@@ -12317,16 +12466,27 @@
         <v>5</v>
       </c>
       <c r="AU14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX14" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <f aca="false">ROUND(AQ14*6/10,0)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AW14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX14" s="6" t="n">
+        <f aca="false">MIN(AW14,AV14)</f>
+        <v>2</v>
+      </c>
+      <c r="AZ14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB14" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
@@ -12441,22 +12601,30 @@
         <v>8</v>
       </c>
       <c r="AV15" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX15" s="1" t="n">
+        <f aca="false">ROUND(AQ15*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AX15" s="6" t="n">
+        <f aca="false">MIN(AW15,AV15)</f>
+        <v>5</v>
+      </c>
+      <c r="AZ15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AY15" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AZ15" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA15" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BC15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BD15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE15" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
@@ -12572,13 +12740,24 @@
         <v>12</v>
       </c>
       <c r="AV16" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY16" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" s="24" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">ROUND(AQ16*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX16" s="6" t="n">
+        <f aca="false">MIN(AW16,AV16)</f>
+        <v>4</v>
+      </c>
+      <c r="AZ16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC16" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>15</v>
       </c>
@@ -12588,26 +12767,21 @@
       <c r="C17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="2"/>
       <c r="E17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="2"/>
       <c r="G17" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H17" s="2"/>
       <c r="I17" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="2"/>
       <c r="L17" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="2"/>
       <c r="N17" s="2" t="n">
         <v>5</v>
       </c>
@@ -12628,11 +12802,9 @@
       <c r="S17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="T17" s="2"/>
       <c r="U17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2"/>
       <c r="W17" s="2" t="n">
         <v>3</v>
       </c>
@@ -12642,7 +12814,6 @@
       <c r="Y17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Z17" s="2"/>
       <c r="AA17" s="2" t="n">
         <v>9</v>
       </c>
@@ -12650,8 +12821,6 @@
         <f aca="false">ROUND(AVERAGE(AA17,Y17,X17,W17,U17,S17,P17),0)</f>
         <v>6</v>
       </c>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
       <c r="AE17" s="2" t="n">
         <v>7</v>
       </c>
@@ -12669,7 +12838,6 @@
         <f aca="false">ROUND(AVERAGE(AH17,AB17),0)</f>
         <v>6</v>
       </c>
-      <c r="AJ17" s="2"/>
       <c r="AK17" s="2" t="s">
         <v>43</v>
       </c>
@@ -12677,10 +12845,10 @@
         <v>9</v>
       </c>
       <c r="AM17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN17" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO17" s="2" t="n">
         <v>1</v>
@@ -12690,33 +12858,41 @@
       </c>
       <c r="AQ17" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(AL17,AM17,AN17,AO17,AP17),0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR17" s="21" t="n">
         <v>6</v>
       </c>
       <c r="AS17" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(AQ17,AR17),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT17" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(AI17,AS17),0)</f>
         <v>6</v>
       </c>
       <c r="AU17" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV17" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="AV17" s="1" t="n">
+        <f aca="false">ROUND(AQ17*6/10,0)</f>
+        <v>4</v>
+      </c>
+      <c r="AW17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX17" s="6" t="n">
+        <f aca="false">MIN(AW17,AV17)</f>
+        <v>2</v>
+      </c>
+      <c r="AZ17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AW17" s="2"/>
-      <c r="AX17" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY17" s="2"/>
-      <c r="BA17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BB17" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
@@ -12831,16 +13007,24 @@
         <v>8</v>
       </c>
       <c r="AV18" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX18" s="1" t="n">
+        <f aca="false">ROUND(AQ18*6/10,0)</f>
         <v>5</v>
       </c>
-      <c r="AY18" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AX18" s="6" t="n">
+        <f aca="false">MIN(AW18,AV18)</f>
+        <v>5</v>
+      </c>
+      <c r="AZ18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC18" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
@@ -12956,13 +13140,23 @@
         <v>12</v>
       </c>
       <c r="AV19" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX19" s="1" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">ROUND(AQ19*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AW19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB19" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
@@ -13080,16 +13274,29 @@
         <v>12</v>
       </c>
       <c r="AV20" s="1" t="n">
+        <f aca="false">ROUND(AQ20*6/10,0)</f>
+        <v>4</v>
+      </c>
+      <c r="AW20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AY20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AW20" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AX20" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BA20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB20" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>19</v>
       </c>
@@ -13180,13 +13387,13 @@
         <v>29</v>
       </c>
       <c r="AL21" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AM21" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN21" s="23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO21" s="2" t="n">
         <v>8</v>
@@ -13196,7 +13403,7 @@
       </c>
       <c r="AQ21" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(AL21,AM21,AN21,AO21,AP21),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR21" s="21" t="n">
         <v>4</v>
@@ -13210,24 +13417,35 @@
         <v>6</v>
       </c>
       <c r="AU21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <f aca="false">ROUND(AQ21*6/10,0)</f>
+        <v>4</v>
+      </c>
+      <c r="AW21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX21" s="6" t="n">
+        <f aca="false">MIN(AW21,AV21)</f>
+        <v>2</v>
+      </c>
+      <c r="AZ21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AV21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY21" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="22" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>5</v>
@@ -13339,9 +13557,20 @@
         <v>5</v>
       </c>
       <c r="AU22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV22" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="AV22" s="1" t="n">
+        <f aca="false">ROUND(AQ22*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AW22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX22" s="6" t="n">
+        <f aca="false">MIN(AW22,AV22)</f>
+        <v>2</v>
+      </c>
+      <c r="AZ22" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -13459,144 +13688,144 @@
         <v>6</v>
       </c>
       <c r="AU23" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV23" s="2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="AV23" s="1" t="n">
+        <f aca="false">ROUND(AQ23*6/10,0)</f>
+        <v>4</v>
+      </c>
+      <c r="AX23" s="6" t="n">
+        <f aca="false">MIN(AW23,AV23)</f>
+        <v>4</v>
+      </c>
+      <c r="AZ23" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" s="24" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>45783</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>45784</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O24" s="2" t="n">
+      <c r="C24" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>46076</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>46080</v>
+      </c>
+      <c r="L24" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O24" s="24" t="n">
         <f aca="false">L24+N24/2</f>
         <v>13.5</v>
       </c>
-      <c r="P24" s="11" t="n">
+      <c r="P24" s="29" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,G24,I24,J24,O24),0)</f>
-        <v>8</v>
-      </c>
-      <c r="Q24" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q24" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="R24" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="S24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2" t="n">
+      <c r="S24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2" t="n">
+      <c r="W24" s="24" t="n">
         <v>5.6</v>
       </c>
-      <c r="X24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB24" s="11" t="n">
+      <c r="X24" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y24" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB24" s="29" t="n">
         <f aca="false">ROUND(AVERAGE(AA24,Y24,X24,W24,U24,S24,P24),0)</f>
         <v>7</v>
       </c>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF24" s="2" t="n">
+      <c r="AE24" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF24" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="AG24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH24" s="2" t="n">
+      <c r="AG24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH24" s="24" t="n">
         <f aca="false">ROUND(AVERAGE(AE24:AG24),0)</f>
         <v>7</v>
       </c>
-      <c r="AI24" s="11" t="n">
+      <c r="AI24" s="29" t="n">
         <f aca="false">ROUND(AVERAGE(AH24,AB24),0)</f>
         <v>7</v>
       </c>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2" t="s">
+      <c r="AK24" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="2"/>
-      <c r="AP24" s="2" t="n">
+      <c r="AM24" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AQ24" s="6" t="n">
+      <c r="AQ24" s="29" t="n">
         <f aca="false">ROUND(AVERAGE(AL24,AM24,AN24,AO24,AP24),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR24" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="AR24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" s="6" t="n">
+      <c r="AS24" s="29" t="n">
         <f aca="false">ROUND(AVERAGE(AQ24,AR24),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AT24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" s="29" t="n">
         <f aca="false">ROUND(AVERAGE(AI24,AS24),0)</f>
         <v>4</v>
       </c>
-      <c r="AU24" s="2" t="s">
+      <c r="AU24" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AX24" s="2"/>
-      <c r="AY24" s="2"/>
-      <c r="AZ24" s="2"/>
-      <c r="BA24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AV24" s="24" t="n">
+        <f aca="false">ROUND(AQ24*6/10,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX24" s="29" t="n">
+        <f aca="false">MIN(AW24,AV24)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
@@ -13715,10 +13944,21 @@
         <v>12</v>
       </c>
       <c r="AV25" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">ROUND(AQ25*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AW25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX25" s="6" t="n">
+        <f aca="false">MIN(AW25,AV25)</f>
+        <v>4</v>
+      </c>
+      <c r="AZ25" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
@@ -13834,16 +14074,27 @@
         <v>12</v>
       </c>
       <c r="AV26" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX26" s="1" t="n">
+        <f aca="false">ROUND(AQ26*6/10,0)</f>
         <v>5</v>
       </c>
-      <c r="AY26" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AW26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX26" s="6" t="n">
+        <f aca="false">MIN(AW26,AV26)</f>
+        <v>4</v>
+      </c>
+      <c r="AZ26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC26" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
@@ -13965,6 +14216,17 @@
       </c>
       <c r="AU27" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="AV27" s="1" t="n">
+        <f aca="false">ROUND(AQ27*6/10,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AW27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX27" s="6" t="n">
+        <f aca="false">MIN(AW27,AV27)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13975,6 +14237,22 @@
       <c r="R28" s="1" t="n">
         <f aca="false">COUNTIF(R3:R27,"P")</f>
         <v>21</v>
+      </c>
+      <c r="AW28" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AX28" s="1" t="n">
+        <f aca="false">COUNTIF(AX4:AX27,"&gt;3")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AW29" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AX29" s="1" t="n">
+        <f aca="false">COUNTIF(AX4:AX27,"&lt;4")</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14070,6 +14348,14 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AX4:AX27">
+    <cfRule type="cellIs" priority="24" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -14102,16 +14388,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -14145,7 +14431,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2</v>
@@ -14170,7 +14456,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2</v>
@@ -14184,7 +14470,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -14204,7 +14490,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -14227,7 +14513,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>8</v>
@@ -14252,7 +14538,7 @@
         <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>7</v>
@@ -14266,7 +14552,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>4</v>
@@ -14300,7 +14586,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
@@ -14325,7 +14611,7 @@
         <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>2</v>
@@ -14339,7 +14625,7 @@
         <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>2</v>
@@ -14359,7 +14645,7 @@
         <v>48</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -14376,7 +14662,7 @@
         <v>48</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>1</v>
@@ -14396,7 +14682,7 @@
         <v>52</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -14421,7 +14707,7 @@
         <v>52</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
@@ -14435,7 +14721,7 @@
         <v>52</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>4</v>
@@ -14449,7 +14735,7 @@
         <v>52</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>3</v>
@@ -14463,7 +14749,7 @@
         <v>52</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>3</v>
@@ -14497,7 +14783,7 @@
         <v>58</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -14522,7 +14808,7 @@
         <v>58</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -14536,7 +14822,7 @@
         <v>58</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>6</v>
@@ -14550,7 +14836,7 @@
         <v>58</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>4</v>
@@ -14564,7 +14850,7 @@
         <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>3</v>
@@ -14584,7 +14870,7 @@
         <v>62</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -14609,7 +14895,7 @@
         <v>62</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -14623,7 +14909,7 @@
         <v>62</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>3</v>
@@ -14637,7 +14923,7 @@
         <v>62</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0</v>
@@ -14651,7 +14937,7 @@
         <v>62</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>0</v>
@@ -14685,7 +14971,7 @@
         <v>70</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>7</v>
@@ -14710,7 +14996,7 @@
         <v>70</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>7</v>
@@ -14724,7 +15010,7 @@
         <v>70</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>3</v>
@@ -14738,7 +15024,7 @@
         <v>70</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>2</v>
@@ -14758,7 +15044,7 @@
         <v>73</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>6</v>
@@ -14783,7 +15069,7 @@
         <v>73</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>5</v>
@@ -14797,7 +15083,7 @@
         <v>73</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>4</v>
@@ -14811,7 +15097,7 @@
         <v>73</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>3</v>
@@ -14825,7 +15111,7 @@
         <v>73</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>2</v>
@@ -14839,7 +15125,7 @@
         <v>73</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>1</v>
@@ -14873,7 +15159,7 @@
         <v>79</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>9</v>
@@ -14898,7 +15184,7 @@
         <v>79</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>8</v>
@@ -14912,7 +15198,7 @@
         <v>79</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>8</v>
@@ -14926,7 +15212,7 @@
         <v>79</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>6</v>
@@ -14940,7 +15226,7 @@
         <v>79</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>3</v>
@@ -14954,7 +15240,7 @@
         <v>79</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>1</v>
@@ -14974,7 +15260,7 @@
         <v>82</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>9</v>
@@ -14999,7 +15285,7 @@
         <v>82</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>5</v>
@@ -15013,7 +15299,7 @@
         <v>82</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>5</v>
@@ -15027,7 +15313,7 @@
         <v>82</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>2</v>
@@ -15041,7 +15327,7 @@
         <v>82</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>0</v>
@@ -15075,7 +15361,7 @@
         <v>88</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>1</v>
@@ -15092,7 +15378,7 @@
         <v>88</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>0</v>
@@ -15103,7 +15389,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>1</v>
@@ -15126,7 +15412,7 @@
         <v>93</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>2</v>
@@ -15143,7 +15429,7 @@
         <v>93</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>0</v>
@@ -15191,7 +15477,7 @@
         <v>104</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>7</v>
@@ -15216,7 +15502,7 @@
         <v>104</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>7</v>
@@ -15230,7 +15516,7 @@
         <v>104</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>5</v>
@@ -15244,7 +15530,7 @@
         <v>104</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>5</v>
@@ -15258,7 +15544,7 @@
         <v>104</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>5</v>
@@ -15272,7 +15558,7 @@
         <v>104</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F68" s="1" t="n">
         <v>4</v>
@@ -15286,7 +15572,7 @@
         <v>104</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>4</v>
@@ -15300,7 +15586,7 @@
         <v>104</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>4</v>
@@ -15314,7 +15600,7 @@
         <v>104</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>2</v>
@@ -15328,7 +15614,7 @@
         <v>104</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>0</v>
@@ -15348,7 +15634,7 @@
         <v>107</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>5</v>
@@ -15373,7 +15659,7 @@
         <v>107</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>4</v>
@@ -15387,7 +15673,7 @@
         <v>107</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>4</v>
@@ -15401,7 +15687,7 @@
         <v>107</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>3</v>
@@ -15415,7 +15701,7 @@
         <v>107</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>3</v>
@@ -15429,7 +15715,7 @@
         <v>107</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>3</v>
@@ -15443,7 +15729,7 @@
         <v>107</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>3</v>
@@ -15457,7 +15743,7 @@
         <v>107</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="F80" s="1" t="n">
         <v>2</v>
@@ -15471,7 +15757,7 @@
         <v>107</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F81" s="1" t="n">
         <v>2</v>
@@ -15485,7 +15771,7 @@
         <v>107</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>2</v>
@@ -15499,7 +15785,7 @@
         <v>107</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="F83" s="1" t="n">
         <v>2</v>
@@ -15513,7 +15799,7 @@
         <v>107</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F84" s="1" t="n">
         <v>2</v>
@@ -15527,7 +15813,7 @@
         <v>107</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F85" s="1" t="n">
         <v>0</v>
@@ -15579,10 +15865,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15599,7 +15885,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>5.6</v>
@@ -15619,7 +15905,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7.4</v>
@@ -15639,7 +15925,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9.8</v>
@@ -15659,7 +15945,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8.8</v>
@@ -15679,7 +15965,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7.8</v>
@@ -15699,7 +15985,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>5</v>
@@ -15719,7 +16005,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>4.6</v>
@@ -15739,7 +16025,7 @@
         <v>52</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>7.2</v>
@@ -15759,7 +16045,7 @@
         <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>3.8</v>
@@ -15779,7 +16065,7 @@
         <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>9.4</v>
@@ -15799,7 +16085,7 @@
         <v>62</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7.6</v>
@@ -15819,7 +16105,7 @@
         <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>5</v>
@@ -15839,7 +16125,7 @@
         <v>70</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8.6</v>
@@ -15859,7 +16145,7 @@
         <v>73</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9.4</v>
@@ -15879,7 +16165,7 @@
         <v>76</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>3</v>
@@ -15899,7 +16185,7 @@
         <v>79</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8.2</v>
@@ -15919,7 +16205,7 @@
         <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>5.4</v>
@@ -15939,7 +16225,7 @@
         <v>85</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
@@ -15959,7 +16245,7 @@
         <v>88</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4.4</v>
@@ -15970,7 +16256,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>92</v>
@@ -15979,7 +16265,7 @@
         <v>91</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>6.8</v>
@@ -15999,7 +16285,7 @@
         <v>93</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>4.4</v>
@@ -16019,7 +16305,7 @@
         <v>96</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>5.6</v>
@@ -16039,7 +16325,7 @@
         <v>101</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -16059,7 +16345,7 @@
         <v>104</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8.8</v>
@@ -16079,7 +16365,7 @@
         <v>107</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>1.8</v>
@@ -16126,16 +16412,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -16155,7 +16441,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -16180,7 +16466,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -16194,7 +16480,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -16208,7 +16494,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
@@ -16222,7 +16508,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -16242,7 +16528,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -16267,7 +16553,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8</v>
@@ -16281,7 +16567,7 @@
         <v>25</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>4</v>
@@ -16295,7 +16581,7 @@
         <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>4</v>
@@ -16315,7 +16601,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -16338,7 +16624,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -16361,7 +16647,7 @@
         <v>38</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -16384,7 +16670,7 @@
         <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -16407,7 +16693,7 @@
         <v>48</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -16430,7 +16716,7 @@
         <v>52</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -16455,7 +16741,7 @@
         <v>52</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
@@ -16469,7 +16755,7 @@
         <v>52</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>6</v>
@@ -16503,7 +16789,7 @@
         <v>58</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -16526,7 +16812,7 @@
         <v>62</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -16549,7 +16835,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -16572,7 +16858,7 @@
         <v>70</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -16595,7 +16881,7 @@
         <v>73</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -16618,7 +16904,7 @@
         <v>76</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -16643,7 +16929,7 @@
         <v>76</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>6</v>
@@ -16657,7 +16943,7 @@
         <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>5</v>
@@ -16671,7 +16957,7 @@
         <v>76</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>2</v>
@@ -16685,7 +16971,7 @@
         <v>76</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2</v>
@@ -16705,7 +16991,7 @@
         <v>79</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>10</v>
@@ -16730,7 +17016,7 @@
         <v>79</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>10</v>
@@ -16744,7 +17030,7 @@
         <v>79</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>3</v>
@@ -16764,7 +17050,7 @@
         <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>10</v>
@@ -16789,7 +17075,7 @@
         <v>82</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>5</v>
@@ -16809,7 +17095,7 @@
         <v>85</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>10</v>
@@ -16834,7 +17120,7 @@
         <v>85</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>6</v>
@@ -16854,7 +17140,7 @@
         <v>88</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>8</v>
@@ -16868,7 +17154,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>1</v>
@@ -16891,7 +17177,7 @@
         <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>10</v>
@@ -16916,7 +17202,7 @@
         <v>93</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>9</v>
@@ -16930,7 +17216,7 @@
         <v>93</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>3</v>
@@ -16950,7 +17236,7 @@
         <v>96</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>10</v>
@@ -16975,7 +17261,7 @@
         <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>9</v>
@@ -16989,7 +17275,7 @@
         <v>96</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>2</v>
@@ -17009,7 +17295,7 @@
         <v>101</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>9</v>
@@ -17034,7 +17320,7 @@
         <v>101</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>8</v>
@@ -17048,7 +17334,7 @@
         <v>101</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>6</v>
@@ -17062,7 +17348,7 @@
         <v>101</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>6</v>
@@ -17076,7 +17362,7 @@
         <v>101</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>3</v>
@@ -17090,7 +17376,7 @@
         <v>101</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>2</v>
@@ -17104,7 +17390,7 @@
         <v>101</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>1</v>
@@ -17124,7 +17410,7 @@
         <v>104</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>10</v>
@@ -17147,7 +17433,7 @@
         <v>107</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>10</v>
@@ -17205,16 +17491,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -17234,7 +17520,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -17257,7 +17543,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -17280,7 +17566,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -17303,7 +17589,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -17340,7 +17626,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -17365,7 +17651,7 @@
         <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -17379,7 +17665,7 @@
         <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>3</v>
@@ -17399,7 +17685,7 @@
         <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -17422,7 +17708,7 @@
         <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -17459,7 +17745,7 @@
         <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -17482,7 +17768,7 @@
         <v>62</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8</v>
@@ -17505,7 +17791,7 @@
         <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -17528,7 +17814,7 @@
         <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -17551,7 +17837,7 @@
         <v>73</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -17574,7 +17860,7 @@
         <v>76</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -17597,7 +17883,7 @@
         <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -17620,7 +17906,7 @@
         <v>82</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -17643,7 +17929,7 @@
         <v>85</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>10</v>
@@ -17666,7 +17952,7 @@
         <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8</v>
@@ -17680,7 +17966,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -17703,7 +17989,7 @@
         <v>93</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -17726,7 +18012,7 @@
         <v>96</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -17749,7 +18035,7 @@
         <v>101</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -17774,7 +18060,7 @@
         <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>8</v>
@@ -17794,7 +18080,7 @@
         <v>104</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -17817,7 +18103,7 @@
         <v>107</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>9</v>
@@ -17964,34 +18250,34 @@
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18443,7 +18729,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>1</v>
@@ -18516,7 +18802,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -18525,7 +18811,7 @@
         <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>138</v>
@@ -19529,7 +19815,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19572,19 +19858,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -19601,10 +19887,10 @@
         <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -19626,10 +19912,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>5</v>
@@ -19646,10 +19932,10 @@
         <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>6</v>
@@ -19671,10 +19957,10 @@
         <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>4</v>
@@ -19685,16 +19971,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>6</v>
@@ -19716,10 +20002,10 @@
         <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>4</v>
@@ -19752,19 +20038,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -19781,10 +20067,10 @@
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -19804,10 +20090,10 @@
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -19829,10 +20115,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -19843,10 +20129,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -19857,10 +20143,10 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
@@ -19877,10 +20163,10 @@
         <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -19902,10 +20188,10 @@
         <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -19916,10 +20202,10 @@
         <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>5</v>
@@ -19930,10 +20216,10 @@
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>2</v>
@@ -19944,10 +20230,10 @@
         <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>2</v>
@@ -19958,10 +20244,10 @@
         <v>31</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -19978,10 +20264,10 @@
         <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>7</v>
@@ -20001,10 +20287,10 @@
         <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -20038,10 +20324,10 @@
         <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -20063,10 +20349,10 @@
         <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -20077,10 +20363,10 @@
         <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -20091,10 +20377,10 @@
         <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8</v>
@@ -20105,10 +20391,10 @@
         <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -20119,10 +20405,10 @@
         <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>5</v>
@@ -20133,10 +20419,10 @@
         <v>53</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>4</v>
@@ -20147,10 +20433,10 @@
         <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>3</v>
@@ -20167,10 +20453,10 @@
         <v>59</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -20192,10 +20478,10 @@
         <v>59</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9</v>
@@ -20226,10 +20512,10 @@
         <v>67</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>1</v>
@@ -20249,10 +20535,10 @@
         <v>71</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>10</v>
@@ -20272,10 +20558,10 @@
         <v>74</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -20297,10 +20583,10 @@
         <v>74</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8</v>
@@ -20311,10 +20597,10 @@
         <v>74</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>3</v>
@@ -20345,10 +20631,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>5</v>
@@ -20370,10 +20656,10 @@
         <v>80</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4</v>
@@ -20384,10 +20670,10 @@
         <v>80</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4</v>
@@ -20398,10 +20684,10 @@
         <v>80</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>3</v>
@@ -20412,10 +20698,10 @@
         <v>80</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>3</v>
@@ -20426,10 +20712,10 @@
         <v>80</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>3</v>
@@ -20446,10 +20732,10 @@
         <v>83</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>8</v>
@@ -20471,10 +20757,10 @@
         <v>83</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>7</v>
@@ -20485,10 +20771,10 @@
         <v>83</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>7</v>
@@ -20499,10 +20785,10 @@
         <v>83</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>6</v>
@@ -20513,10 +20799,10 @@
         <v>83</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>5</v>
@@ -20527,10 +20813,10 @@
         <v>83</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>0</v>
@@ -20589,10 +20875,10 @@
         <v>97</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>10</v>
@@ -20614,10 +20900,10 @@
         <v>97</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>9</v>
@@ -20634,10 +20920,10 @@
         <v>102</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>10</v>
@@ -20659,10 +20945,10 @@
         <v>102</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>9</v>
@@ -20673,10 +20959,10 @@
         <v>102</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>8</v>
@@ -20687,10 +20973,10 @@
         <v>102</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>4</v>
@@ -20701,10 +20987,10 @@
         <v>102</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>1</v>
@@ -20721,10 +21007,10 @@
         <v>105</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>10</v>
@@ -20746,10 +21032,10 @@
         <v>105</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>9</v>
@@ -20760,10 +21046,10 @@
         <v>105</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>8</v>
@@ -20774,10 +21060,10 @@
         <v>105</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>6</v>
@@ -20788,10 +21074,10 @@
         <v>105</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>3</v>
@@ -20816,7 +21102,7 @@
         <v>25</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20863,16 +21149,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>138</v>
@@ -20883,7 +21169,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>8</v>
@@ -20897,7 +21183,7 @@
         <v>63</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>8</v>
@@ -20911,7 +21197,7 @@
         <v>108</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>8</v>
@@ -20933,7 +21219,7 @@
         <v>108</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>4</v>
@@ -20944,7 +21230,7 @@
         <v>108</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>4</v>
@@ -20955,7 +21241,7 @@
         <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>4</v>
@@ -20966,7 +21252,7 @@
         <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
@@ -20977,7 +21263,7 @@
         <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>3</v>
@@ -20988,7 +21274,7 @@
         <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>2</v>
@@ -21023,13 +21309,13 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21037,10 +21323,10 @@
         <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -21051,10 +21337,10 @@
         <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -21065,10 +21351,10 @@
         <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>9</v>
@@ -21104,19 +21390,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>138</v>
@@ -21147,10 +21433,10 @@
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -21172,10 +21458,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>7</v>
@@ -21186,10 +21472,10 @@
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>6</v>
@@ -21200,10 +21486,10 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>6</v>
@@ -21214,10 +21500,10 @@
         <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>4</v>
@@ -21234,10 +21520,10 @@
         <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8</v>
@@ -21259,10 +21545,10 @@
         <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>6</v>
@@ -21273,10 +21559,10 @@
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>6</v>
@@ -21293,10 +21579,10 @@
         <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8</v>
@@ -21316,10 +21602,10 @@
         <v>45</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8</v>
@@ -21341,10 +21627,10 @@
         <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -21361,10 +21647,10 @@
         <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -21386,10 +21672,10 @@
         <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -21400,10 +21686,10 @@
         <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>2</v>
@@ -21414,10 +21700,10 @@
         <v>49</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -21434,10 +21720,10 @@
         <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -21457,10 +21743,10 @@
         <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -21480,10 +21766,10 @@
         <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>6</v>
@@ -21503,10 +21789,10 @@
         <v>67</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8</v>
@@ -21526,10 +21812,10 @@
         <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -21549,10 +21835,10 @@
         <v>74</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -21572,10 +21858,10 @@
         <v>77</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>6</v>
@@ -21595,10 +21881,10 @@
         <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8</v>
@@ -21620,10 +21906,10 @@
         <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>8</v>
@@ -21634,10 +21920,10 @@
         <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>7</v>
@@ -21648,10 +21934,10 @@
         <v>80</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>7</v>
@@ -21668,10 +21954,10 @@
         <v>83</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -21693,10 +21979,10 @@
         <v>83</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8</v>
@@ -21707,10 +21993,10 @@
         <v>83</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>8</v>
@@ -21721,10 +22007,10 @@
         <v>83</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>6</v>
@@ -21741,10 +22027,10 @@
         <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -21766,10 +22052,10 @@
         <v>86</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>4</v>
@@ -21786,10 +22072,10 @@
         <v>89</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>9</v>
@@ -21811,10 +22097,10 @@
         <v>89</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>8</v>
@@ -21825,10 +22111,10 @@
         <v>89</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>2</v>
@@ -21845,10 +22131,10 @@
         <v>94</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>9</v>
@@ -21870,10 +22156,10 @@
         <v>94</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>8</v>
@@ -21884,10 +22170,10 @@
         <v>94</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>7</v>
@@ -21898,10 +22184,10 @@
         <v>94</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>6</v>
@@ -21912,10 +22198,10 @@
         <v>94</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>6</v>
@@ -21926,10 +22212,10 @@
         <v>94</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>5</v>
@@ -21940,10 +22226,10 @@
         <v>94</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>2</v>
@@ -21974,10 +22260,10 @@
         <v>102</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>7</v>
@@ -21997,10 +22283,10 @@
         <v>105</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>8</v>
@@ -22020,10 +22306,10 @@
         <v>108</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>5</v>
@@ -22037,7 +22323,7 @@
         <v>25</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
